--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487397_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487397_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2268</v>
+        <v>2.912</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9993</v>
+        <v>2.0587</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2275</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4679</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9321</v>
+        <v>0.6172</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3194</v>
+        <v>0.3788</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6127</v>
+        <v>0.2385</v>
       </c>
       <c r="V2" t="n">
         <v>0.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5612</v>
+        <v>0.4589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="G3" t="n">
         <v>0.8035</v>
@@ -688,13 +688,13 @@
         <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.178</v>
+        <v>-0.2536</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1911</v>
+        <v>-0.2935</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0131</v>
+        <v>0.0399</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1718</v>
+        <v>0.2474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.337</v>
+        <v>0.4393</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1652</v>
+        <v>-0.1919</v>
       </c>
       <c r="G4" t="n">
         <v>1.4379</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.326</v>
+        <v>-0.2504</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4993</v>
+        <v>-0.397</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1733</v>
+        <v>0.1466</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3318</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0319</v>
+        <v>-0.7679</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>-0.2471</v>
@@ -844,10 +844,10 @@
         <v>3.1336</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1364</v>
+        <v>0.4005</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2776</v>
+        <v>0.5417</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1411</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>X. RUBIN CARBALLEIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7346</v>
+        <v>-1.9108</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0086</v>
+        <v>-1.156</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7432</v>
+        <v>-0.7548</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7614</v>
+        <v>-0.2048</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9234</v>
+        <v>-0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.838</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9333</v>
+        <v>0.0608</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0442</v>
+        <v>0.0204</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8891</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.6947</v>
+        <v>-0.2656</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9676</v>
+        <v>-0.1344</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7271</v>
+        <v>-0.1313</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7626</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7359</v>
+        <v>-0.7268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.2376</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8111</v>
+        <v>-0.4892</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. RUBIN CARBALLEIRA</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.991</v>
+        <v>-1.9868</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.156</v>
+        <v>0.8633</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.835</v>
+        <v>-2.8501</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2048</v>
+        <v>-2.7614</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.114</v>
+        <v>-1.9234</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.838</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0608</v>
+        <v>0.9333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0204</v>
+        <v>0.0442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0404</v>
+        <v>0.8891</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2656</v>
+        <v>-3.6947</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1344</v>
+        <v>-1.9676</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1313</v>
+        <v>-1.7271</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9792</v>
+        <v>1.7626</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.9881</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2376</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5694</v>
+        <v>-0.9181</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1344</v>
+        <v>-2.2322</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8632</v>
+        <v>-1.0678</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2713</v>
+        <v>-1.1643</v>
       </c>
       <c r="G8" t="n">
         <v>0.0154</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3445</v>
+        <v>-0.4423</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5516</v>
+        <v>-0.4446</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8260999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1635</v>
+        <v>-4.0761</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1449</v>
+        <v>-2.1644</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0186</v>
+        <v>-1.9117</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5353</v>
@@ -1156,13 +1156,13 @@
         <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9819</v>
+        <v>-0.8946</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3727</v>
+        <v>-0.3923</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6092</v>
+        <v>-0.5023</v>
       </c>
       <c r="V9" t="n">
         <v>0.9412</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8547</v>
+        <v>-7.1303</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7989</v>
+        <v>-5.2082</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0558</v>
+        <v>-1.9221</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2139</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1903</v>
+        <v>-0.466</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4799</v>
+        <v>0.0706</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6702</v>
+        <v>-0.5365</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6464</v>
+        <v>-7.8406</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3197</v>
+        <v>-6.5673</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3268</v>
+        <v>-1.2733</v>
       </c>
       <c r="G11" t="n">
         <v>-5.264</v>
@@ -1312,13 +1312,13 @@
         <v>2.9377</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2603</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6034</v>
+        <v>0.3558</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3431</v>
+        <v>-0.2897</v>
       </c>
       <c r="V11" t="n">
         <v>1.2742</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.5324</v>
+        <v>-22.2354</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.1614</v>
+        <v>-12.8642</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.3713</v>
+        <v>-9.371</v>
       </c>
       <c r="G12" t="n">
         <v>-14.9833</v>
@@ -1390,13 +1390,13 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2348</v>
+        <v>-2.9379</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3380999999999997</v>
+        <v>-0.04120000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8966</v>
+        <v>-2.8965</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3769</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7266</v>
+        <v>8.3849</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6806</v>
+        <v>5.0899</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0461</v>
+        <v>3.2951</v>
       </c>
       <c r="G13" t="n">
         <v>5.6669</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1005</v>
+        <v>0.5578</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1735</v>
+        <v>0.2358</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0731</v>
+        <v>0.322</v>
       </c>
       <c r="V13" t="n">
         <v>1.3768</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8218</v>
+        <v>3.3453</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0132</v>
+        <v>-0.5249</v>
       </c>
       <c r="F14" t="n">
-        <v>3.835</v>
+        <v>3.8701</v>
       </c>
       <c r="G14" t="n">
         <v>3.0268</v>
@@ -1546,13 +1546,13 @@
         <v>3.1336</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1072</v>
+        <v>1.6306</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3098</v>
+        <v>0.7981</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7974</v>
+        <v>0.8325</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3329</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. LATAS CHICO</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2763</v>
+        <v>3.0865</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2622</v>
+        <v>3.6356</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0141</v>
+        <v>-0.5491</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3907</v>
+        <v>2.5066</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9226</v>
+        <v>2.3294</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3133</v>
+        <v>0.1772</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6488</v>
+        <v>3.7014</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2695</v>
+        <v>2.3273</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6207</v>
+        <v>1.3741</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0395</v>
+        <v>-1.1948</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3468</v>
+        <v>0.0021</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6926</v>
+        <v>-1.1969</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7419</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0642</v>
+        <v>0.3471</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6148</v>
+        <v>0.13</v>
       </c>
       <c r="U15" t="n">
+        <v>0.2172</v>
+      </c>
+      <c r="V15" t="n">
         <v>-0.5507</v>
       </c>
-      <c r="V15" t="n">
-        <v>-0.9412</v>
-      </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0653</v>
+        <v>2.8756</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0449</v>
+        <v>2.0513</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9796</v>
+        <v>0.8243</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5066</v>
+        <v>0.659</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3294</v>
+        <v>0.4866</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1772</v>
+        <v>0.1724</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7014</v>
+        <v>2.0466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3273</v>
+        <v>0.5512</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3741</v>
+        <v>1.4954</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1948</v>
+        <v>-1.3875</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0021</v>
+        <v>-0.0646</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1969</v>
+        <v>-1.3229</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.326</v>
+        <v>0.0622</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5393</v>
+        <v>0.0047</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2133</v>
+        <v>0.0575</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8283</v>
+        <v>2.4164</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0389</v>
+        <v>0.3459</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7895</v>
+        <v>2.0705</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2888</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9005</v>
+        <v>1.4886</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4558</v>
+        <v>0.7628</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4447</v>
+        <v>0.7258</v>
       </c>
       <c r="V17" t="n">
         <v>1.2166</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. LATAS CHICO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6503</v>
+        <v>2.2888</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2326</v>
+        <v>-0.3752</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4178</v>
+        <v>2.664</v>
       </c>
       <c r="G18" t="n">
-        <v>0.659</v>
+        <v>0.3907</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4866</v>
+        <v>-0.9226</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1724</v>
+        <v>1.3133</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0466</v>
+        <v>-0.6488</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5512</v>
+        <v>-1.2695</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4954</v>
+        <v>0.6207</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3875</v>
+        <v>1.0395</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0646</v>
+        <v>0.3468</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3229</v>
+        <v>0.6926</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.163</v>
+        <v>1.0767</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.9775</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3491</v>
+        <v>0.0993</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4767</v>
+        <v>2.0428</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0881</v>
+        <v>1.8049</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3886</v>
+        <v>0.2379</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1195</v>
+        <v>2.0732</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5737</v>
+        <v>0.3202</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5458</v>
+        <v>1.7531</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3675</v>
+        <v>3.1951</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3675</v>
+        <v>0.114</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.0812</v>
       </c>
       <c r="M19" t="n">
-        <v>0.752</v>
+        <v>-1.1219</v>
       </c>
       <c r="N19" t="n">
         <v>0.2062</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5458</v>
+        <v>-1.3281</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7004</v>
+        <v>0.8693</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2794</v>
+        <v>0.4887</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.421</v>
+        <v>0.3805</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0785</v>
+        <v>1.9367</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1909</v>
+        <v>0.0881</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1124</v>
+        <v>1.8486</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0732</v>
+        <v>1.1195</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3202</v>
+        <v>0.5737</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7531</v>
+        <v>0.5458</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1951</v>
+        <v>0.3675</v>
       </c>
       <c r="K20" t="n">
-        <v>0.114</v>
+        <v>0.3675</v>
       </c>
       <c r="L20" t="n">
-        <v>3.0812</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1219</v>
+        <v>0.752</v>
       </c>
       <c r="N20" t="n">
         <v>0.2062</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3281</v>
+        <v>0.5458</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.095</v>
+        <v>-0.2404</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1253</v>
+        <v>-0.2794</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0302</v>
+        <v>0.039</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2754</v>
+        <v>0.6659</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5626</v>
+        <v>1.3729</v>
       </c>
       <c r="E21" t="n">
         <v>-0.4946</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0572</v>
+        <v>1.8675</v>
       </c>
       <c r="G21" t="n">
         <v>3.1607</v>
@@ -2092,13 +2092,13 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1695</v>
+        <v>-0.3592</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0378</v>
+        <v>-0.2275</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0576</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4977</v>
+        <v>0.0988</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6048</v>
+        <v>-1.1954</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1071</v>
+        <v>1.2942</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3254</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1723</v>
+        <v>0.4242</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1606</v>
+        <v>0.2488</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0117</v>
+        <v>0.1754</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4563</v>
+        <v>-2.5872</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0544</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.402</v>
+        <v>-1.5328</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0061</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2376</v>
+        <v>0.1067</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3388</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5764</v>
+        <v>0.4455</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>22.5324</v>
+        <v>25.2615</v>
       </c>
       <c r="E24" t="n">
         <v>9.3712</v>
       </c>
       <c r="F24" t="n">
-        <v>13.1614</v>
+        <v>15.8903</v>
       </c>
       <c r="G24" t="n">
         <v>14.9831</v>
@@ -2326,13 +2326,13 @@
         <v>18.6055</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2348</v>
+        <v>5.9636</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8964</v>
+        <v>2.8965</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3382000000000001</v>
+        <v>3.0672</v>
       </c>
       <c r="V24" t="n">
         <v>1.3769</v>
